--- a/docs/DemoBlaze-Test-Cases.xlsx
+++ b/docs/DemoBlaze-Test-Cases.xlsx
@@ -3829,7 +3829,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="62" customHeight="1">
+    <row r="34" ht="90" customHeight="1">
       <c r="A34" s="21" t="inlineStr">
         <is>
           <t>LGN-033</t>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>Login fails with 'User does not exist.'; no authentication bypass, no server error, no SQL error surfaced</t>
+          <t>The attempt is rejected and no session is created; no authentication bypass, no server error, no SQL error text surfaced. Note the rejection wording is not asserted: DemoBlaze is a public sandbox and this username is already registered by another tester, so the message depends on state the suite does not own</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr"/>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="48" customHeight="1">
+    <row r="35" ht="76" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
           <t>LGN-034</t>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="J35" s="27" t="inlineStr">
         <is>
-          <t>The payload is treated as text; no script executes and nothing is rendered as HTML in the error message or the welcome label</t>
+          <t>The payload is treated as text; no script executes (its own alert never fires) and nothing is rendered as HTML in the error message or the welcome label. The rejection wording is not asserted — this username is already registered on the shared sandbox</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr"/>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="48" customHeight="1">
+    <row r="36" ht="62" customHeight="1">
       <c r="A36" s="21" t="inlineStr">
         <is>
           <t>LGN-035</t>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>The request is handled gracefully — a normal 'User does not exist.' error, no 500 and no unhandled client error</t>
+          <t>The request is handled gracefully — a normal rejection, no 500 and no unhandled client error. The rejection wording is not asserted, since this username already exists on the shared sandbox</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr"/>
